--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -1091,10 +1091,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>kmicb.engagecomms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>kmicb.comms@nhs.net</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>https://www.kentandmedway.icb.nhs.uk/contact-us</t>
@@ -1113,7 +1117,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mailto link points here; display text shows kmicb.engagecomms@nhs.net â€” either should work.</t>
+          <t>Mailto link points here; display text shows kmicb.engagecomms@nhs.net â€” either should work. | press primary updated 2026-05-29 from [https://www.kentandmedway.icb.nhs.uk/contact-us]; prior value kmicb.comms@nhs.net moved to _alt</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -1758,10 +1758,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>bobicb.media@nhs.net</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>frimleyicb.public@nhs.net</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>https://thamesvalley.icb.nhs.uk/contact-us</t>
@@ -1769,10 +1773,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>frimleyicb.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>SCWCSU.FOI@nhs.net</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>https://thamesvalley.icb.nhs.uk/contact-us/freedom-of-information</t>
@@ -1780,7 +1788,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Predecessor Frimley general address â€” new merged Thames Valley ICB has no dedicated press email yet.; Email obfuscated on page (joomla-hidden-mail base64); decoded from page source. Handled by South Central and West CSU</t>
+          <t>Predecessor Frimley general address â€” new merged Thames Valley ICB has no dedicated press email yet.; Email obfuscated on page (joomla-hidden-mail base64); decoded from page source. Handled by South Central and West CSU | press primary updated 2026-06-06 from https://thamesvalley.icb.nhs.uk/contact-us (dedicated media address bobicb.media@nhs.net now shown; prior frimleyicb.public@nhs.net to _alt); foi primary updated 2026-06-06 from https://thamesvalley.icb.nhs.uk/contact-us/freedom-of-information (frimleyicb.foi@nhs.net now shown; prior SCWCSU.FOI@nhs.net to _alt).</t>
         </is>
       </c>
     </row>
